--- a/Data/Input/ProjectNames.xlsx
+++ b/Data/Input/ProjectNames.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SalesBot\Desktop\UiPath\CustomerCare\TitleDeed_TrnasferNOC\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07036F6-2151-49CF-8673-3C050BEBDCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AFC155-C3AF-4150-904B-7B4595A0FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{84D2D992-6E50-4305-A157-9E8169CC2196}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{84D2D992-6E50-4305-A157-9E8169CC2196}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BankNames" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="148">
   <si>
     <t>DLD Sub Set</t>
   </si>
@@ -396,6 +397,93 @@
   </si>
   <si>
     <t>Rawda, Parkview, Parkside, Parkside Apartments</t>
+  </si>
+  <si>
+    <t>AJMAN BANK</t>
+  </si>
+  <si>
+    <t>Aafaq Islamic Finance</t>
+  </si>
+  <si>
+    <t>United Arab Bank</t>
+  </si>
+  <si>
+    <t>Mashreq Al Islami Finance Company PJSC(179126)</t>
+  </si>
+  <si>
+    <t>Abu Dhabi Finance</t>
+  </si>
+  <si>
+    <t>National Bank Of Fujairah</t>
+  </si>
+  <si>
+    <t>Samba Bank</t>
+  </si>
+  <si>
+    <t>Al Hilal Bank</t>
+  </si>
+  <si>
+    <t>Union National Bank</t>
+  </si>
+  <si>
+    <t>Emirates Development Bank</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>Mashreq Bank</t>
+  </si>
+  <si>
+    <t>Emirates Islamic Bank</t>
+  </si>
+  <si>
+    <t>Standard Chartered Bank</t>
+  </si>
+  <si>
+    <t>Commercial Bank International</t>
+  </si>
+  <si>
+    <t>Noor Bank PJSC.</t>
+  </si>
+  <si>
+    <t>Commercial Bank of Dubai</t>
+  </si>
+  <si>
+    <t>Emirates NBD Bank PJSC</t>
+  </si>
+  <si>
+    <t>RAK  Bank</t>
+  </si>
+  <si>
+    <t>Bank of Baroda</t>
+  </si>
+  <si>
+    <t>Amlak Finance PJSC.</t>
+  </si>
+  <si>
+    <t>Dubai Islamic Bank</t>
+  </si>
+  <si>
+    <t>ADCB</t>
+  </si>
+  <si>
+    <t>Arab Bank</t>
+  </si>
+  <si>
+    <t>First Abu Dhabi Bank</t>
+  </si>
+  <si>
+    <t>Abu Dhabi Islamic Bank</t>
+  </si>
+  <si>
+    <t>Habib Bank AG Zurich</t>
+  </si>
+  <si>
+    <t>Sharjah Islamic Bank</t>
+  </si>
+  <si>
+    <t>Bank Names</t>
   </si>
 </sst>
 </file>
@@ -1333,4 +1421,162 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6EFE16-9B49-432F-A9D2-8A8CA76F1978}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>